--- a/data/export/2026-09-30-182路.xlsx
+++ b/data/export/2026-09-30-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,33 +693,37 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -743,32 +751,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:17</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -776,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,17 +812,17 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
@@ -820,13 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -854,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -887,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,33 +931,37 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -965,32 +989,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -998,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1022,17 +1050,17 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1042,13 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1148,7 +1180,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1159,7 +1191,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1302,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1413,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1389,22 +1421,22 @@
       <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>沪A55712D</t>
+          <t>沪A02126A</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1437,12 +1469,12 @@
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1456,7 +1488,7 @@
       <c r="T9" s="2" t="inlineStr"/>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
@@ -1492,7 +1524,1014 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>70.0</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-30-182路.xlsx
+++ b/data/export/2026-09-30-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC18"/>
+  <dimension ref="A1:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1011,12 +1011,12 @@
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1219,32 +1219,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -1252,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1276,33 +1280,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1330,32 +1338,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1363,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1387,33 +1399,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1513,7 +1529,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1552,32 +1568,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -1585,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1609,33 +1629,37 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1663,32 +1687,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -1696,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1720,33 +1748,37 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1774,32 +1806,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1807,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1831,33 +1867,37 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1918,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2029,7 +2069,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2144,7 +2184,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,7 +2295,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,7 +2406,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2428,22 +2468,22 @@
       <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>沪A67026D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2481,7 +2521,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2495,43 +2535,959 @@
       <c r="T18" s="2" t="inlineStr"/>
       <c r="U18" s="2" t="inlineStr">
         <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>08:15</t>
         </is>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W18" s="2" t="inlineStr">
+      <c r="W19" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X18" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y18" s="2" t="inlineStr">
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z18" s="2" t="inlineStr">
+      <c r="Z19" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr"/>
-      <c r="AC18" s="2" t="inlineStr">
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
         <is>
           <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-30-182路.xlsx
+++ b/data/export/2026-09-30-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC26"/>
+  <dimension ref="A1:AC32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,12 +832,12 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1697,24 +1697,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1925,32 +1925,36 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1958,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:12</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1982,33 +1986,37 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2036,32 +2044,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2069,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2093,37 +2105,37 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2151,32 +2163,36 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -2184,7 +2200,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2208,33 +2224,37 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2262,32 +2282,36 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2295,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2319,33 +2343,37 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2373,32 +2401,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2406,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2430,37 +2462,37 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2488,32 +2520,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2521,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2545,17 +2581,17 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
@@ -2565,12 +2601,12 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2636,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2690,7 +2726,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2751,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2790,7 +2826,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2862,7 +2898,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2973,7 +3009,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3027,7 +3063,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3124,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3142,7 +3178,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3203,7 +3239,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3257,7 +3293,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3318,7 +3354,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3367,12 +3403,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3469,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3487,7 +3523,693 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>78.5</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
           <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>09:12</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-30-182路.xlsx
+++ b/data/export/2026-09-30-182路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1185,13 +1185,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1375,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1490,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1605,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1724,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1843,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1897,7 +1901,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2200,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2319,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2438,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2672,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2754,32 +2758,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2787,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2811,17 +2819,17 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -2831,13 +2839,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3009,7 +3021,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3124,7 +3136,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3239,7 +3251,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3354,7 +3366,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3469,7 +3481,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3523,7 +3535,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3699,7 +3711,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3814,7 +3826,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3929,7 +3941,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4044,7 +4056,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4159,7 +4171,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4203,13 +4215,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB32" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-30-182路.xlsx
+++ b/data/export/2026-09-30-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC32"/>
+  <dimension ref="A1:AC40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1299,22 +1299,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,22 +1418,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,18 +1533,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1653,17 +1657,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1767,22 +1771,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1886,22 +1890,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2020,7 +2024,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2139,7 +2143,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2243,7 +2247,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2258,7 +2262,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2377,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2496,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2600,7 +2604,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2676,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2715,7 +2719,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2730,7 +2734,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2768,12 +2772,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>09:43</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
@@ -2795,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2844,12 +2848,12 @@
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2877,32 +2881,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -2910,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2934,33 +2942,37 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2988,32 +3000,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:54</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -3021,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3045,37 +3061,37 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3103,32 +3119,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3136,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3160,37 +3180,37 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3218,32 +3238,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -3251,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3275,17 +3299,17 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3295,17 +3319,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3333,32 +3357,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -3366,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3390,37 +3418,37 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3448,32 +3476,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:23</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3481,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3505,37 +3537,37 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3596,7 +3628,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:12</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3650,7 +3682,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3765,7 +3797,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3826,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3865,7 +3897,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3880,7 +3912,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3941,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3995,7 +4027,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4088,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4110,7 +4142,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4118,22 +4150,22 @@
       <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>沪A67026D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4171,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4185,47 +4217,967 @@
       <c r="T32" s="2" t="inlineStr"/>
       <c r="U32" s="2" t="inlineStr">
         <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>74.5</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
           <t>10:15</t>
         </is>
       </c>
-      <c r="V32" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W32" s="2" t="inlineStr">
+      <c r="W33" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X32" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y32" s="2" t="inlineStr">
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z32" s="2" t="inlineStr">
+      <c r="Z33" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
+      <c r="AA33" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB32" s="2" t="inlineStr">
-        <is>
-          <t>88.0</t>
-        </is>
-      </c>
-      <c r="AC32" s="2" t="inlineStr">
-        <is>
-          <t>11/14</t>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>79.5</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>81.5</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-30-182路.xlsx
+++ b/data/export/2026-09-30-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC40"/>
+  <dimension ref="A1:AC46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,12 +832,12 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,22 +1180,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2128,22 +2128,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2252,17 +2252,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,22 +2366,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2485,22 +2485,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2838,22 +2838,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3595,32 +3595,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3628,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3652,17 +3656,17 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
@@ -3672,12 +3676,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3710,32 +3714,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3743,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3767,37 +3775,37 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3825,32 +3833,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -3858,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3882,17 +3894,17 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
@@ -3902,17 +3914,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3940,32 +3952,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -3973,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3997,37 +4013,37 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4055,32 +4071,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4088,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4112,37 +4132,37 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4170,32 +4190,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4203,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4227,17 +4251,17 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
@@ -4247,12 +4271,12 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4285,32 +4309,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4318,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4342,37 +4370,37 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4400,32 +4428,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4433,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4457,17 +4489,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4477,17 +4509,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4587,7 +4619,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4663,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4702,7 +4734,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4717,7 +4749,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4778,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4832,7 +4864,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4893,7 +4925,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4947,7 +4979,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5008,7 +5040,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5062,7 +5094,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5070,22 +5102,22 @@
       <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>沪A68397D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -5118,12 +5150,12 @@
       <c r="M40" s="2" t="inlineStr"/>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>07:02</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5137,47 +5169,737 @@
       <c r="T40" s="2" t="inlineStr"/>
       <c r="U40" s="2" t="inlineStr">
         <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>76.3</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="V40" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W40" s="2" t="inlineStr">
+      <c r="W41" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X40" s="2" t="inlineStr">
+      <c r="X41" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y40" s="2" t="inlineStr">
+      <c r="Y41" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z40" s="2" t="inlineStr">
+      <c r="Z41" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB40" s="2" t="inlineStr">
-        <is>
-          <t>86.0</t>
-        </is>
-      </c>
-      <c r="AC40" s="2" t="inlineStr">
-        <is>
-          <t>12/14</t>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-30-182路.xlsx
+++ b/data/export/2026-09-30-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC46"/>
+  <dimension ref="A1:AC51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1304,17 +1304,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1538,17 +1538,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,22 +1771,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1895,17 +1895,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2133,17 +2133,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2247,22 +2247,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2962,17 +2962,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3081,17 +3081,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3200,17 +3200,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3433,22 +3433,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3557,17 +3557,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3795,17 +3795,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3909,22 +3909,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4438,24 +4438,24 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4547,32 +4547,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -4580,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4604,17 +4608,17 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -4624,17 +4628,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4662,32 +4666,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:49</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -4695,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4719,17 +4727,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4739,17 +4747,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4777,32 +4785,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4810,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4834,17 +4846,17 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
@@ -4854,17 +4866,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4892,32 +4904,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -4925,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4949,37 +4965,37 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -5007,32 +5023,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5040,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5064,17 +5084,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5084,17 +5104,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5122,32 +5142,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5155,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5179,17 +5203,17 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5199,17 +5223,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5237,32 +5261,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -5270,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5294,37 +5322,37 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5385,7 +5413,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5439,7 +5467,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5554,7 +5582,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -5615,7 +5643,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5669,7 +5697,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5730,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5774,17 +5802,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -5845,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5889,17 +5917,592 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>75.3</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB46" s="2" t="inlineStr">
-        <is>
-          <t>81.0</t>
-        </is>
-      </c>
-      <c r="AC46" s="2" t="inlineStr">
-        <is>
-          <t>11/14</t>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>79.7</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>75.5</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-30-182路.xlsx
+++ b/data/export/2026-09-30-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC51"/>
+  <dimension ref="A1:AC56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1304,17 +1304,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,14 +1418,14 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
           <t>79.7</t>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,22 +1533,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,14 +1890,14 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>78.0</t>
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,22 +2366,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2843,17 +2843,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2957,22 +2957,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3081,17 +3081,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3195,14 +3195,14 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>79.7</t>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3552,14 +3552,14 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
           <t>78.0</t>
@@ -3567,7 +3567,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4028,22 +4028,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4390,17 +4390,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4623,22 +4623,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4747,17 +4747,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4861,14 +4861,14 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
           <t>79.7</t>
@@ -4876,7 +4876,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5099,14 +5099,14 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
           <t>78.0</t>
@@ -5114,7 +5114,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5152,24 +5152,24 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5228,7 +5228,7 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5380,32 +5380,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5413,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5437,17 +5441,17 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5457,7 +5461,7 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
@@ -5467,7 +5471,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5495,32 +5499,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5528,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5552,37 +5560,37 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5610,32 +5618,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5643,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5667,17 +5679,17 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
@@ -5687,17 +5699,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5725,32 +5737,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>66分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -5758,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5782,37 +5798,37 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -5840,32 +5856,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -5873,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5897,17 +5917,17 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5917,17 +5937,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5988,7 +6008,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6103,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6142,7 +6162,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6218,7 +6238,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6272,7 +6292,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6333,7 +6353,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6387,7 +6407,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -6395,22 +6415,22 @@
       <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>沪A66513D</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>13:35</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -6443,12 +6463,12 @@
       <c r="M51" s="2" t="inlineStr"/>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6462,47 +6482,622 @@
       <c r="T51" s="2" t="inlineStr"/>
       <c r="U51" s="2" t="inlineStr">
         <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>76.7</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
           <t>13:35</t>
         </is>
       </c>
-      <c r="V51" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W51" s="2" t="inlineStr">
+      <c r="W52" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X51" s="2" t="inlineStr">
+      <c r="X52" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y51" s="2" t="inlineStr">
+      <c r="Y52" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z51" s="2" t="inlineStr">
+      <c r="Z52" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
+      <c r="AA52" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB51" s="2" t="inlineStr">
+      <c r="AB52" s="2" t="inlineStr">
         <is>
           <t>75.5</t>
         </is>
       </c>
-      <c r="AC51" s="2" t="inlineStr">
+      <c r="AC52" s="2" t="inlineStr">
         <is>
           <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>79.7</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-30-182路.xlsx
+++ b/data/export/2026-09-30-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC56"/>
+  <dimension ref="A1:AC62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,14 +708,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>76.2</t>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,17 +827,17 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,14 +946,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
           <t>79.0</t>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1652,14 +1652,14 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
           <t>75.0</t>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2014,12 +2014,12 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2128,14 +2128,14 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
           <t>76.2</t>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2252,17 +2252,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2371,17 +2371,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2485,14 +2485,14 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
           <t>79.0</t>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2604,17 +2604,17 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2719,22 +2719,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3086,12 +3086,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3314,14 +3314,14 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
           <t>75.0</t>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3676,12 +3676,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3790,14 +3790,14 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
           <t>76.2</t>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3914,17 +3914,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4033,17 +4033,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4147,14 +4147,14 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
           <t>79.0</t>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4266,17 +4266,17 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4504,22 +4504,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5218,14 +5218,14 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
           <t>76.2</t>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5342,17 +5342,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5456,14 +5456,14 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
           <t>79.0</t>
@@ -5471,7 +5471,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5580,17 +5580,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5866,24 +5866,24 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5942,12 +5942,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5975,32 +5975,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -6008,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6032,17 +6036,17 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
@@ -6052,12 +6056,12 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>74.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6090,32 +6094,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6123,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6147,17 +6155,17 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -6167,12 +6175,12 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6205,32 +6213,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -6238,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6262,17 +6274,17 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
@@ -6282,17 +6294,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6320,32 +6332,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6353,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6377,32 +6393,32 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6435,32 +6451,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -6468,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6492,17 +6512,17 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6512,17 +6532,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6550,32 +6570,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6583,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6607,37 +6631,37 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -6698,7 +6722,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6813,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6852,7 +6876,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6867,7 +6891,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6928,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6972,12 +6996,12 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7043,7 +7067,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7101,6 +7125,696 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>76.2</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>73.2</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>74.0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>79.7</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-09-30-182路.xlsx
+++ b/data/export/2026-09-30-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC62"/>
+  <dimension ref="A1:AC68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1538,12 +1538,12 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,17 +1890,17 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3200,17 +3200,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3552,17 +3552,17 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4866,17 +4866,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4980,7 +4980,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5099,17 +5099,17 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5585,12 +5585,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
@@ -6461,12 +6461,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6537,12 +6537,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6592,12 +6592,12 @@
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6689,32 +6689,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -6722,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6746,17 +6750,17 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6766,12 +6770,12 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6804,32 +6808,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6837,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6861,17 +6869,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6881,17 +6889,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7034,32 +7042,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7067,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7091,32 +7103,32 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7182,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7221,7 +7233,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7264,32 +7276,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7297,7 +7313,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7321,17 +7337,17 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7341,7 +7357,7 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
@@ -7412,7 +7428,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7451,7 +7467,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7527,7 +7543,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7642,7 +7658,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7696,7 +7712,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -7757,7 +7773,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7801,17 +7817,707 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>77.5</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>76.8</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>77.5</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB62" s="2" t="inlineStr">
-        <is>
-          <t>79.7</t>
-        </is>
-      </c>
-      <c r="AC62" s="2" t="inlineStr">
-        <is>
-          <t>13/14</t>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>78.3</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>74.5</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>76.2</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-30-182路.xlsx
+++ b/data/export/2026-09-30-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC68"/>
+  <dimension ref="A1:AC75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,17 +827,17 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2247,14 +2247,14 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
           <t>78.8</t>
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,14 +2366,14 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
           <t>75.2</t>
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2604,17 +2604,17 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3200,17 +3200,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3909,14 +3909,14 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
           <t>78.8</t>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4028,14 +4028,14 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
           <t>75.2</t>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4266,17 +4266,17 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4509,17 +4509,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4866,17 +4866,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5337,14 +5337,14 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
           <t>78.8</t>
@@ -5352,7 +5352,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5575,14 +5575,14 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
           <t>75.2</t>
@@ -5590,7 +5590,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6289,14 +6289,14 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
           <t>78.8</t>
@@ -6304,7 +6304,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6408,17 +6408,17 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6527,14 +6527,14 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
           <t>75.2</t>
@@ -6542,7 +6542,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6651,17 +6651,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6889,17 +6889,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6999,7 +6999,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7286,24 +7286,24 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -7313,7 +7313,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7352,17 +7352,17 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7395,32 +7395,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -7428,7 +7432,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7452,17 +7456,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7472,12 +7476,12 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7510,32 +7514,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7543,7 +7551,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7567,17 +7575,17 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
@@ -7587,17 +7595,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>74.0</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -7658,7 +7666,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7697,7 +7705,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7740,32 +7748,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7773,7 +7785,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7797,17 +7809,17 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -7817,17 +7829,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -7888,7 +7900,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7927,7 +7939,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -7960,7 +7972,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -8003,7 +8015,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8017,7 +8029,7 @@
       <c r="T64" s="2" t="inlineStr"/>
       <c r="U64" s="2" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="V64" s="2" t="inlineStr">
@@ -8118,7 +8130,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8157,7 +8169,7 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
@@ -8172,7 +8184,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8233,7 +8245,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8287,7 +8299,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -8305,7 +8317,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -8348,7 +8360,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8362,7 +8374,7 @@
       <c r="T67" s="2" t="inlineStr"/>
       <c r="U67" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="V67" s="2" t="inlineStr">
@@ -8402,7 +8414,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -8410,22 +8422,22 @@
       <c r="A68" s="2" t="inlineStr"/>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>沪A12050A</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -8458,12 +8470,12 @@
       <c r="M68" s="2" t="inlineStr"/>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8477,47 +8489,852 @@
       <c r="T68" s="2" t="inlineStr"/>
       <c r="U68" s="2" t="inlineStr">
         <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>78.8</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
           <t>16:20</t>
         </is>
       </c>
-      <c r="V68" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W68" s="2" t="inlineStr">
+      <c r="W69" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X68" s="2" t="inlineStr">
+      <c r="X69" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y68" s="2" t="inlineStr">
+      <c r="Y69" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z68" s="2" t="inlineStr">
+      <c r="Z69" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB68" s="2" t="inlineStr">
-        <is>
-          <t>75.0</t>
-        </is>
-      </c>
-      <c r="AC68" s="2" t="inlineStr">
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>75.7</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
         <is>
           <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>80.3</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>73.4</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>75.2</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>76.8</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>78.3</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-30-182路.xlsx
+++ b/data/export/2026-09-30-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC75"/>
+  <dimension ref="A1:AC83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1304,17 +1304,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,22 +1418,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,22 +1771,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3081,17 +3081,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3195,22 +3195,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3433,22 +3433,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4623,7 +4623,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4747,17 +4747,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4861,22 +4861,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4980,22 +4980,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5699,12 +5699,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5813,7 +5813,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5937,17 +5937,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6051,22 +6051,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6289,7 +6289,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6542,7 +6542,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6765,7 +6765,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6884,22 +6884,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6999,7 +6999,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7133,7 +7133,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7194,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7233,7 +7233,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7313,7 +7313,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7486,7 +7486,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7720,7 +7720,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -7758,24 +7758,24 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7824,22 +7824,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -7867,32 +7867,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -7900,7 +7904,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7924,17 +7928,17 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
@@ -7944,17 +7948,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8015,7 +8019,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8054,7 +8058,7 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -8069,7 +8073,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8097,32 +8101,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8130,7 +8138,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8154,17 +8162,17 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
@@ -8174,12 +8182,12 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8212,32 +8220,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -8245,7 +8257,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8269,37 +8281,37 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>74.5</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8372,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8399,7 +8411,7 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8475,7 +8487,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8514,7 +8526,7 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
@@ -8529,7 +8541,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8590,7 +8602,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8644,7 +8656,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -8705,7 +8717,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8744,7 +8756,7 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
@@ -8759,7 +8771,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8832,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8935,7 +8947,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8989,7 +9001,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -9050,7 +9062,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9104,7 +9116,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -9112,22 +9124,22 @@
       <c r="A74" s="2" t="inlineStr"/>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>沪A67353D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -9160,12 +9172,12 @@
       <c r="M74" s="2" t="inlineStr"/>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>06:12</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9214,12 +9226,12 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -9227,7 +9239,7 @@
       <c r="A75" s="2" t="inlineStr"/>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>沪A67026D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -9237,7 +9249,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -9275,12 +9287,12 @@
       <c r="M75" s="2" t="inlineStr"/>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:12</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9294,47 +9306,967 @@
       <c r="T75" s="2" t="inlineStr"/>
       <c r="U75" s="2" t="inlineStr">
         <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="V75" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W75" s="2" t="inlineStr">
+      <c r="W76" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X75" s="2" t="inlineStr">
+      <c r="X76" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y75" s="2" t="inlineStr">
+      <c r="Y76" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z75" s="2" t="inlineStr">
+      <c r="Z76" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA75" s="2" t="inlineStr">
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>78.8</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>71.5</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>76.2</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>17:35</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>87.4</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>78.8</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>77.5</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB75" s="2" t="inlineStr">
-        <is>
-          <t>78.3</t>
-        </is>
-      </c>
-      <c r="AC75" s="2" t="inlineStr">
-        <is>
-          <t>10/14</t>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>80.3</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>17:22</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>76.2</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-30-182路.xlsx
+++ b/data/export/2026-09-30-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC83"/>
+  <dimension ref="A1:AC87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1657,17 +1657,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2252,17 +2252,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2366,7 +2366,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2604,22 +2604,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3319,17 +3319,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3914,17 +3914,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4266,22 +4266,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5342,17 +5342,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5575,7 +5575,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5947,7 +5947,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6066,7 +6066,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6294,17 +6294,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6408,22 +6408,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6542,7 +6542,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6661,7 +6661,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7133,7 +7133,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -7194,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7352,22 +7352,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7432,7 +7432,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7476,17 +7476,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7705,7 +7705,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7720,7 +7720,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -7785,7 +7785,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7943,7 +7943,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8019,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8192,7 +8192,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8257,7 +8257,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8311,7 +8311,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -8454,32 +8454,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -8487,7 +8491,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8511,17 +8515,17 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
@@ -8531,17 +8535,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -8569,32 +8573,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -8602,7 +8610,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8626,17 +8634,17 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
@@ -8646,17 +8654,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -8717,7 +8725,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8771,7 +8779,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -8799,32 +8807,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8832,7 +8844,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8856,37 +8868,37 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -8947,7 +8959,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8986,7 +8998,7 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
@@ -9001,7 +9013,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -9062,7 +9074,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9101,7 +9113,7 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
@@ -9116,7 +9128,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -9177,7 +9189,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9231,7 +9243,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -9292,7 +9304,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9331,7 +9343,7 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9346,7 +9358,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -9407,7 +9419,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9461,7 +9473,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -9522,7 +9534,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9637,7 +9649,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9691,7 +9703,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -9752,7 +9764,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9867,7 +9879,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9911,17 +9923,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>81.2</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -9982,7 +9994,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10036,7 +10048,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -10097,7 +10109,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10151,7 +10163,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -10212,7 +10224,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10266,7 +10278,467 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>77.3</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
           <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>75.2</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-30-182路.xlsx
+++ b/data/export/2026-09-30-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC87"/>
+  <dimension ref="A1:AC95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1304,17 +1304,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,22 +1771,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1890,22 +1890,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2128,17 +2128,17 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2247,17 +2247,17 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2843,17 +2843,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3081,17 +3081,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3433,22 +3433,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3552,22 +3552,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3790,17 +3790,17 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3909,17 +3909,17 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4390,17 +4390,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4623,7 +4623,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4747,17 +4747,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4980,22 +4980,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5099,22 +5099,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5218,17 +5218,17 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5298,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5337,17 +5337,17 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5699,17 +5699,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5813,7 +5813,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5937,17 +5937,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6051,22 +6051,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6289,17 +6289,17 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6423,7 +6423,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6661,7 +6661,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6765,7 +6765,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7118,22 +7118,22 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -7194,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7233,17 +7233,17 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7313,7 +7313,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7367,7 +7367,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -7551,7 +7551,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7590,7 +7590,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7705,7 +7705,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7720,7 +7720,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7785,7 +7785,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7824,7 +7824,7 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7948,17 +7948,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8019,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8058,22 +8058,22 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8182,17 +8182,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -8257,7 +8257,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8296,22 +8296,22 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8411,17 +8411,17 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8530,17 +8530,17 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8664,7 +8664,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -8725,7 +8725,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8779,7 +8779,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8844,7 +8844,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8898,7 +8898,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8998,7 +8998,7 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
@@ -9013,7 +9013,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -9074,7 +9074,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9189,7 +9189,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9228,7 +9228,7 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9243,7 +9243,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -9271,32 +9271,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>105分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -9304,7 +9308,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9328,17 +9332,17 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
@@ -9348,17 +9352,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -9386,32 +9390,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9419,7 +9427,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9443,17 +9451,17 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
@@ -9463,17 +9471,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -9534,7 +9542,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9573,7 +9581,7 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9616,32 +9624,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>113分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -9649,7 +9661,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9673,37 +9685,37 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA78" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -9764,7 +9776,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9803,7 +9815,7 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -9846,32 +9858,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:26</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -9879,7 +9895,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9903,32 +9919,32 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA80" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>81.2</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -9961,32 +9977,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:23</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9994,7 +10014,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10018,37 +10038,37 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -10109,7 +10129,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10163,7 +10183,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -10191,32 +10211,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:34</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10224,7 +10248,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10248,32 +10272,32 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
@@ -10296,7 +10320,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -10339,7 +10363,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10353,7 +10377,7 @@
       <c r="T84" s="2" t="inlineStr"/>
       <c r="U84" s="2" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="V84" s="2" t="inlineStr">
@@ -10393,7 +10417,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -10454,7 +10478,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10569,7 +10593,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10608,7 +10632,7 @@
       </c>
       <c r="Z86" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA86" s="2" t="inlineStr">
@@ -10623,7 +10647,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -10631,22 +10655,22 @@
       <c r="A87" s="2" t="inlineStr"/>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>沪A67353D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>19:05</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -10679,12 +10703,12 @@
       <c r="M87" s="2" t="inlineStr"/>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>06:12</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10698,47 +10722,967 @@
       <c r="T87" s="2" t="inlineStr"/>
       <c r="U87" s="2" t="inlineStr">
         <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>76.5</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>71.5</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
           <t>19:05</t>
         </is>
       </c>
-      <c r="V87" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W87" s="2" t="inlineStr">
+      <c r="W89" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X87" s="2" t="inlineStr">
+      <c r="X89" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y87" s="2" t="inlineStr">
+      <c r="Y89" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z87" s="2" t="inlineStr">
+      <c r="Z89" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA87" s="2" t="inlineStr">
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>82.5</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB87" s="2" t="inlineStr">
-        <is>
-          <t>78.0</t>
-        </is>
-      </c>
-      <c r="AC87" s="2" t="inlineStr">
-        <is>
-          <t>8/14</t>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>87.4</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>82.3</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>80.6</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>76.8</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>19:22</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-30-182路.xlsx
+++ b/data/export/2026-09-30-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC95"/>
+  <dimension ref="A1:AC98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,12 +832,12 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1299,22 +1299,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1538,12 +1538,12 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,22 +1771,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2014,17 +2014,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2371,17 +2371,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3076,22 +3076,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3200,17 +3200,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3433,22 +3433,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3676,17 +3676,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3800,12 +3800,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4033,17 +4033,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4152,12 +4152,12 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4271,12 +4271,12 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4742,22 +4742,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4866,17 +4866,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4980,22 +4980,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5228,12 +5228,12 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5417,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5580,17 +5580,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5932,22 +5932,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6051,22 +6051,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6175,17 +6175,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6289,7 +6289,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6413,12 +6413,12 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6532,17 +6532,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6661,7 +6661,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6770,12 +6770,12 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6889,17 +6889,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6960,7 +6960,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7004,17 +7004,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7133,7 +7133,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7194,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7243,12 +7243,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7357,12 +7357,12 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7551,7 +7551,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7605,7 +7605,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7710,12 +7710,12 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7829,17 +7829,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7943,22 +7943,22 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA63" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8019,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -8257,7 +8257,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8296,22 +8296,22 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8491,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8530,7 +8530,7 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
@@ -8545,7 +8545,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -8725,7 +8725,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8769,17 +8769,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -8844,7 +8844,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -8959,7 +8959,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9118,17 +9118,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9243,7 +9243,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9347,22 +9347,22 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA75" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -9481,7 +9481,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -9542,7 +9542,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9586,12 +9586,12 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9661,7 +9661,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9700,22 +9700,22 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA78" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -9776,7 +9776,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9820,17 +9820,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -9895,7 +9895,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9934,7 +9934,7 @@
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
@@ -9949,7 +9949,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -10014,7 +10014,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10068,7 +10068,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -10096,32 +10096,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:46</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>105分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10129,7 +10133,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10153,17 +10157,17 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
@@ -10173,17 +10177,17 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -10221,12 +10225,12 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>19:34</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
@@ -10248,7 +10252,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10297,12 +10301,12 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -10330,32 +10334,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:46</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10363,7 +10371,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10387,17 +10395,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10407,12 +10415,12 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
@@ -10445,32 +10453,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -10478,7 +10490,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10502,17 +10514,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10522,17 +10534,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -10560,32 +10572,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10593,7 +10609,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10617,17 +10633,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10637,12 +10653,12 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
@@ -10708,7 +10724,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>19:52</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10762,7 +10778,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -10790,32 +10806,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10823,7 +10843,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:11</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10847,17 +10867,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10867,12 +10887,12 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
@@ -10905,32 +10925,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -10938,7 +10962,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10962,37 +10986,37 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA89" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -11020,32 +11044,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:37</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11053,7 +11081,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11077,17 +11105,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11097,17 +11125,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -11135,32 +11163,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -11168,7 +11200,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11192,37 +11224,37 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA91" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -11283,7 +11315,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11337,7 +11369,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -11398,7 +11430,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11447,12 +11479,12 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -11513,7 +11545,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11552,7 +11584,7 @@
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
@@ -11567,7 +11599,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -11628,7 +11660,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:22</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11672,17 +11704,362 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
           <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>81.6</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>07:02</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-30-182路.xlsx
+++ b/data/export/2026-09-30-182路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1304,17 +1304,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1781,12 +1781,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1895,17 +1895,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2133,17 +2133,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3081,17 +3081,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3557,17 +3557,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3795,17 +3795,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3914,12 +3914,12 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -4108,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4152,12 +4152,12 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4747,17 +4747,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4822,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4871,12 +4871,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5104,17 +5104,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5223,17 +5223,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5342,12 +5342,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5937,17 +5937,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6294,12 +6294,12 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6661,7 +6661,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6894,12 +6894,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -7079,7 +7079,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7123,17 +7123,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -7194,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7238,17 +7238,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7486,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7605,7 +7605,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7710,12 +7710,12 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7948,17 +7948,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8019,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8063,17 +8063,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -8257,7 +8257,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8306,12 +8306,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8372,7 +8372,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8416,17 +8416,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8491,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8535,12 +8535,12 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
@@ -8664,7 +8664,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
@@ -9243,7 +9243,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9352,17 +9352,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9710,12 +9710,12 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -9776,7 +9776,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -9895,7 +9895,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9939,12 +9939,12 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10058,17 +10058,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -10252,7 +10252,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10296,17 +10296,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -10609,7 +10609,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10653,12 +10653,12 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
@@ -10778,7 +10778,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -10962,7 +10962,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11006,17 +11006,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -11054,12 +11054,12 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>20:37</t>
+          <t>20:38</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
@@ -11081,7 +11081,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -11173,24 +11173,24 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:46</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -11200,7 +11200,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11249,12 +11249,12 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -11282,32 +11282,36 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11315,7 +11319,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11339,17 +11343,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11359,17 +11363,17 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>80.6</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -11397,32 +11401,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:57</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11430,7 +11438,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11454,17 +11462,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11474,17 +11482,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -11512,32 +11520,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -11545,7 +11557,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11569,17 +11581,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11589,12 +11601,12 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
@@ -11627,32 +11639,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:26</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11660,7 +11676,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11684,17 +11700,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11704,12 +11720,12 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
@@ -11742,32 +11758,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -11775,7 +11795,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11799,17 +11819,17 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11819,17 +11839,17 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -11890,7 +11910,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11939,12 +11959,12 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -12005,7 +12025,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12049,12 +12069,12 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>83.1</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">

--- a/data/export/2026-09-30-182路.xlsx
+++ b/data/export/2026-09-30-182路.xlsx
@@ -1260,7 +1260,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1776,17 +1776,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3086,12 +3086,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3438,17 +3438,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4941,7 +4941,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4985,17 +4985,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5942,12 +5942,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6056,17 +6056,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7953,12 +7953,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8257,7 +8257,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8301,17 +8301,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8491,7 +8491,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -9308,7 +9308,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9357,12 +9357,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -9661,7 +9661,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9705,17 +9705,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -9895,7 +9895,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10962,7 +10962,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11011,12 +11011,12 @@
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -11200,7 +11200,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11244,17 +11244,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -11557,7 +11557,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11768,24 +11768,24 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>21:42</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -11795,7 +11795,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11844,12 +11844,12 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>80.4</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -11877,32 +11877,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:04</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -11910,7 +11914,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11934,17 +11938,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -11954,17 +11958,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -12025,7 +12029,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
